--- a/public/data/announcement.xlsx
+++ b/public/data/announcement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E8BE85-DAD1-4708-9811-DF81A4B806F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8E247B-856B-44EA-B807-016A50972E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
   <si>
     <t>title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1810,6 +1810,37 @@
 But there might be not so much features to update. _(:3」∠)_
 Sorry for the inconvenience. ＞＜</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超かぐや姫！を見よう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まだ見てない人は早う見よう！
+もう見た人はもう一回見よう！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>没看过的赶紧去看！
+看过的再去刷一遍！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>都给我去看超时空辉夜姬！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Go to Watch the COSMIC PRINCESS KAGUYA！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Who haven't watched it yet go to watch it right now！
+Who have watched it go to watch it twice！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2221,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="32.75" style="2" customWidth="1"/>
@@ -2243,111 +2274,122 @@
     </row>
     <row r="2" spans="1:3" ht="144" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="144" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="144" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" ht="144" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="144" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="144" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="144" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="144" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="144" customHeight="1">
       <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="144" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="144" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:3" ht="144" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="134.44999999999999" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:3" ht="134.44999999999999" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="124.15" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:3" ht="124.15" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2359,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44EB5A59-D915-436D-B84E-1CE7D4DA204C}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="32.75" style="2" customWidth="1"/>
@@ -2380,112 +2422,123 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="144" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="144" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="144" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" ht="144" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="144" customHeight="1">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:3" ht="144" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="144" customHeight="1">
-      <c r="A5" s="8" t="s">
+    <row r="6" spans="1:3" ht="144" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="144" customHeight="1">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:3" ht="144" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="144" customHeight="1">
-      <c r="A7" s="7" t="s">
+    <row r="8" spans="1:3" ht="144" customHeight="1">
+      <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="144" customHeight="1">
-      <c r="A8" s="6" t="s">
+    <row r="9" spans="1:3" ht="144" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="144" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:3" ht="144" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="134.44999999999999" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:3" ht="134.44999999999999" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="124.15" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:3" ht="124.15" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2497,10 +2550,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96133E2C-5762-42BD-AAC7-6C9B4BA0CCEA}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="35.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="46.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="142.875" style="2" customWidth="1"/>
     <col min="3" max="3" width="23.875" style="2" customWidth="1"/>
     <col min="4" max="16384" width="8.875" style="2"/>
@@ -2518,112 +2571,123 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="144" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="144" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="144" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" ht="144" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="144" customHeight="1">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:3" ht="144" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="144" customHeight="1">
-      <c r="A5" s="8" t="s">
+    <row r="6" spans="1:3" ht="144" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="144" customHeight="1">
-      <c r="A6" s="6" t="s">
+    <row r="7" spans="1:3" ht="144" customHeight="1">
+      <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="144" customHeight="1">
-      <c r="A7" s="7" t="s">
+    <row r="8" spans="1:3" ht="144" customHeight="1">
+      <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="144" customHeight="1">
-      <c r="A8" s="6" t="s">
+    <row r="9" spans="1:3" ht="144" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="144" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:3" ht="144" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="141.6" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:3" ht="141.6" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="124.15" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:3" ht="124.15" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/public/data/announcement.xlsx
+++ b/public/data/announcement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8E247B-856B-44EA-B807-016A50972E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336D2A77-FEDB-4FA7-807D-D22DAC26839B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -1817,11 +1817,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>まだ見てない人は早う見よう！
-もう見た人はもう一回見よう！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2026-03-01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1841,6 +1836,11 @@
   <si>
     <t>Who haven't watched it yet go to watch it right now！
 Who have watched it go to watch it twice！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まだ見てない人は早う見よう！
+既に見た人はもう一回見よう！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2277,10 +2277,10 @@
         <v>72</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="144" customHeight="1">
@@ -2423,13 +2423,13 @@
     </row>
     <row r="2" spans="1:3" ht="144" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="144" customHeight="1">
@@ -2572,13 +2572,13 @@
     </row>
     <row r="2" spans="1:3" ht="144" customHeight="1">
       <c r="A2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="144" customHeight="1">

--- a/public/data/announcement.xlsx
+++ b/public/data/announcement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336D2A77-FEDB-4FA7-807D-D22DAC26839B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E0B5B1-92C3-403A-A3F4-924F42E97861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2396,6 +2396,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/public/data/announcement.xlsx
+++ b/public/data/announcement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E0B5B1-92C3-403A-A3F4-924F42E97861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22DDC15-F40C-4309-A3F8-443FE2B2262C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="79">
   <si>
     <t>title</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2252,144 +2252,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="142.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.875" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="2"/>
+    <col min="1" max="2" width="32.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="46.375" style="2" customWidth="1"/>
+    <col min="4" max="6" width="142.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="144" customHeight="1">
+    <row r="2" spans="1:7" ht="144" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="144" customHeight="1">
+    <row r="3" spans="1:7" ht="144" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="144" customHeight="1">
+    <row r="4" spans="1:7" ht="144" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="144" customHeight="1">
+    <row r="5" spans="1:7" ht="144" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="144" customHeight="1">
+    <row r="6" spans="1:7" ht="144" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="144" customHeight="1">
+    <row r="7" spans="1:7" ht="144" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="144" customHeight="1">
+    <row r="8" spans="1:7" ht="144" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="144" customHeight="1">
+    <row r="9" spans="1:7" ht="144" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="144" customHeight="1">
+    <row r="10" spans="1:7" ht="144" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="134.44999999999999" customHeight="1">
+    <row r="11" spans="1:7" ht="134.44999999999999" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="124.15" customHeight="1">
+    <row r="12" spans="1:7" ht="124.15" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
